--- a/package-output-map.xlsx
+++ b/package-output-map.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/floswald/git/JPEtemplate/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/econ0763/Downloads/JPE/JPE-Tincani-20230441/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067DD2C7-24FE-2447-A5A8-8F6542C7C06E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FA5860D-B1C4-C04E-9D24-35FBA01D3E88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="21900" windowHeight="12060" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17360" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="404">
   <si>
     <t>Data Preparation Program</t>
   </si>
@@ -36,6 +36,132 @@
     <t>Reproduced?</t>
   </si>
   <si>
+    <t>code/stata/1.Clean_GPA.do</t>
+  </si>
+  <si>
+    <t>Cleaned high-school GPA inputs</t>
+  </si>
+  <si>
+    <t>code/stata/2.Clean_simce.do</t>
+  </si>
+  <si>
+    <t>Cleaned SIMCE/baseline ability inputs</t>
+  </si>
+  <si>
+    <t>code/stata/3.Clean_docentes.do</t>
+  </si>
+  <si>
+    <t>Cleaned teacher survey inputs</t>
+  </si>
+  <si>
+    <t>code/stata/4.Clean_jefes.do</t>
+  </si>
+  <si>
+    <t>Cleaned principal survey inputs</t>
+  </si>
+  <si>
+    <t>code/stata/5.Generate_applic_admi_uni_selectivity.do</t>
+  </si>
+  <si>
+    <t>Application, admission, university, and selectivity variables</t>
+  </si>
+  <si>
+    <t>code/stata/6.Merge_basefinal.do</t>
+  </si>
+  <si>
+    <t>Merged experimental base data and inverse probability weights</t>
+  </si>
+  <si>
+    <t>code/stata/7.Clean_basefinal.do</t>
+  </si>
+  <si>
+    <t>Cleaned final high-school analysis variables</t>
+  </si>
+  <si>
+    <t>code/stata/8.Clean_academic_data.do</t>
+  </si>
+  <si>
+    <t>Academic outcomes and saved geocoding-based variables</t>
+  </si>
+  <si>
+    <t>code/stata/11.Data_for_model_estimation_rescale.do</t>
+  </si>
+  <si>
+    <t>Model-estimation data and outside-model parameter inputs</t>
+  </si>
+  <si>
+    <t>code/stata/12.Empirical_coefficients_rescale.do</t>
+  </si>
+  <si>
+    <t>Empirical coefficients for model estimation</t>
+  </si>
+  <si>
+    <t>code/stata/13.Create_bootstrap.do</t>
+  </si>
+  <si>
+    <t>Bootstrap input samples</t>
+  </si>
+  <si>
+    <t>code/julia/14.Estimation_rescale_fast_adjw_20shocks.jl</t>
+  </si>
+  <si>
+    <t>estimation_theta_rescale_fast_adjw_20shocks.csv</t>
+  </si>
+  <si>
+    <t>code/julia/15.Simulations_rescale.jl - 18.Simulations_effpers_and_PACE_revision2round_baseline.jl</t>
+  </si>
+  <si>
+    <t>Main simulation outputs</t>
+  </si>
+  <si>
+    <t>code/julia/bootstrap/Estimation_s_bootstrap*.jl</t>
+  </si>
+  <si>
+    <t>estimation_theta_s_bootstrap1.csv - estimation_theta_s_bootstrap50.csv</t>
+  </si>
+  <si>
+    <t>code/python/add_params_ses_to_table_csv_estimates.py</t>
+  </si>
+  <si>
+    <t>structural_model_estimates_edited.tex</t>
+  </si>
+  <si>
+    <t>code/stata/19.Calculate_bias_RE_cutoff.do</t>
+  </si>
+  <si>
+    <t>Belief-bias calculations for rational-expectations cutoff</t>
+  </si>
+  <si>
+    <t>code/julia/20.Simulations_top5.jl - 24.Simulations_top25.jl</t>
+  </si>
+  <si>
+    <t>Alternative-cutoff simulation outputs</t>
+  </si>
+  <si>
+    <t>code/julia/25.Estimation_rescale_fast_3types.jl</t>
+  </si>
+  <si>
+    <t>estimation_theta_rescale_fast_3types.csv</t>
+  </si>
+  <si>
+    <t>code/julia/26.Simulations_rescale_3types.jl</t>
+  </si>
+  <si>
+    <t>Three-type simulation outputs</t>
+  </si>
+  <si>
+    <t>code/stata/27.Tables_Figures_model_numbers.do</t>
+  </si>
+  <si>
+    <t>Final tables and figures under tex/output</t>
+  </si>
+  <si>
+    <t>code/stata/27b.In_text_numbers.do</t>
+  </si>
+  <si>
+    <t>tex/output/in_text_numbers/in_text_numbers.log</t>
+  </si>
+  <si>
     <t>Figure/Table #</t>
   </si>
   <si>
@@ -45,14 +171,1079 @@
     <t>Line Number</t>
   </si>
   <si>
+    <t>Reproduced?</t>
+  </si>
+  <si>
+    <t>Table 1 - sample_balance.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>Table 2 - Overview of Data</t>
+  </si>
+  <si>
+    <t>code/tex/data.tex</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Figure 1 - histogram_simce_control_all.png; histogram_simce_controltop15_all.png</t>
+  </si>
+  <si>
+    <t>code/stata/10.Figures.do</t>
+  </si>
+  <si>
+    <t>24; 34</t>
+  </si>
+  <si>
+    <t>Table 3 - summary_stats_outcomes.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>191</t>
+  </si>
+  <si>
+    <t>Figure 2 - TE_over_time_enrolled_SUA_in_experimental_schools.png</t>
+  </si>
+  <si>
+    <t>code/stata/10.Figures.do</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>Table 4 - TE_pre_college_outcomes.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>262</t>
+  </si>
+  <si>
+    <t>Figure 3 - heterog_effects_effort_score.png</t>
+  </si>
+  <si>
+    <t>code/stata/10.Figures.do</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>Table 5 - summary_beliefs.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>316</t>
+  </si>
+  <si>
+    <t>Table 6 - TE_pre_college_outcomes_perceived_dist_cutoff_f.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>378</t>
+  </si>
+  <si>
+    <t>Figure 4 - histogram_p_graduate_T_C.png</t>
+  </si>
+  <si>
+    <t>code/stata/10.Figures.do</t>
+  </si>
+  <si>
+    <t>289</t>
+  </si>
+  <si>
+    <t>Figure 5 - returns_effort_PSUGPA_raw_answers_comb.png</t>
+  </si>
+  <si>
+    <t>code/stata/10.Figures.do</t>
+  </si>
+  <si>
+    <t>304</t>
+  </si>
+  <si>
+    <t>Table 7 - causal_correlational_returns_eff_pers.tex</t>
+  </si>
+  <si>
+    <t>code/stata/27.Tables_Figures_model_numbers.do</t>
+  </si>
+  <si>
+    <t>257</t>
+  </si>
+  <si>
+    <t>Figure 6 - TE_over_time_enrolled_SUA.png</t>
+  </si>
+  <si>
+    <t>code/stata/27.Tables_Figures_model_numbers.do</t>
+  </si>
+  <si>
+    <t>2823</t>
+  </si>
+  <si>
+    <t>Figure 7 - TE_effort_byrank_fe_model1.png</t>
+  </si>
+  <si>
+    <t>code/stata/27.Tables_Figures_model_numbers.do</t>
+  </si>
+  <si>
+    <t>2872</t>
+  </si>
+  <si>
+    <t>Table 8 - TE_pre_college_outcomes_model_fit.tex</t>
+  </si>
+  <si>
+    <t>code/stata/27.Tables_Figures_model_numbers.do</t>
+  </si>
+  <si>
+    <t>476</t>
+  </si>
+  <si>
+    <t>Table 9 - simulated_ATEs_RE.tex</t>
+  </si>
+  <si>
+    <t>code/stata/27.Tables_Figures_model_numbers.do</t>
+  </si>
+  <si>
+    <t>2700</t>
+  </si>
+  <si>
+    <t>Figure 8 - TE_over_time_enrolled_SUA_count.png</t>
+  </si>
+  <si>
+    <t>code/stata/27.Tables_Figures_model_numbers.do</t>
+  </si>
+  <si>
+    <t>3207</t>
+  </si>
+  <si>
+    <t>Table 10 - simulated_ATEs.tex</t>
+  </si>
+  <si>
+    <t>code/stata/27.Tables_Figures_model_numbers.do</t>
+  </si>
+  <si>
+    <t>1176</t>
+  </si>
+  <si>
+    <t>Figure 9 - Counterfactual_multiple_cutoffs_avg_individual_TE.png</t>
+  </si>
+  <si>
+    <t>code/stata/27.Tables_Figures_model_numbers.do</t>
+  </si>
+  <si>
+    <t>3622</t>
+  </si>
+  <si>
+    <t>Figure B1 - enrollment_SUA_gradient.png</t>
+  </si>
+  <si>
+    <t>code/stata/10.Figures.do</t>
+  </si>
+  <si>
+    <t>329</t>
+  </si>
+  <si>
+    <t>Figure B2 - hist_majors_pace_regular_slots.png</t>
+  </si>
+  <si>
+    <t>code/stata/10.Figures.do</t>
+  </si>
+  <si>
+    <t>352</t>
+  </si>
+  <si>
+    <t>Figure B3 - hist_quality_pace_regular_slots.png</t>
+  </si>
+  <si>
+    <t>code/stata/10.Figures.do</t>
+  </si>
+  <si>
+    <t>377</t>
+  </si>
+  <si>
+    <t>Figure B4 - timeline.png</t>
+  </si>
+  <si>
+    <t>code/tex/timeline.png</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Figure B5 - sit_PSU_prepared_admitted_lpoly_inpaper.png</t>
+  </si>
+  <si>
+    <t>code/stata/10.Figures.do</t>
+  </si>
+  <si>
+    <t>395</t>
+  </si>
+  <si>
+    <t>Figure B6 - PSU_belief_actual_distribution.png</t>
+  </si>
+  <si>
+    <t>code/stata/10.Figures.do</t>
+  </si>
+  <si>
+    <t>417</t>
+  </si>
+  <si>
+    <t>Figure B7 - GPA_hist.png</t>
+  </si>
+  <si>
+    <t>code/stata/10.Figures.do</t>
+  </si>
+  <si>
+    <t>425</t>
+  </si>
+  <si>
+    <t>Figure B8 - discrimination.png</t>
+  </si>
+  <si>
+    <t>code/stata/10.Figures.do</t>
+  </si>
+  <si>
+    <t>438</t>
+  </si>
+  <si>
+    <t>Figure B9 - beliefs_hetero_byranksimce_inpaper.png</t>
+  </si>
+  <si>
+    <t>code/stata/10.Figures.do</t>
+  </si>
+  <si>
+    <t>470</t>
+  </si>
+  <si>
+    <t>Figure B10 - heterog_effects_p_grad.png</t>
+  </si>
+  <si>
+    <t>code/stata/10.Figures.do</t>
+  </si>
+  <si>
+    <t>555</t>
+  </si>
+  <si>
+    <t>Figure B11 - admission_regular_PSU_fit.png</t>
+  </si>
+  <si>
+    <t>code/stata/10.Figures.do</t>
+  </si>
+  <si>
+    <t>593</t>
+  </si>
+  <si>
+    <t>Figure B12 - admission_quality_fit_rescale.png</t>
+  </si>
+  <si>
+    <t>code/stata/10.Figures.do</t>
+  </si>
+  <si>
+    <t>693</t>
+  </si>
+  <si>
+    <t>Figure B13 - TE_perceived_returns_effort_REC_REPT.png</t>
+  </si>
+  <si>
+    <t>code/stata/27.Tables_Figures_model_numbers.do</t>
+  </si>
+  <si>
+    <t>3677</t>
+  </si>
+  <si>
+    <t>Figure B14 - effects_info_CC_bysimce.png</t>
+  </si>
+  <si>
+    <t>code/stata/27.Tables_Figures_model_numbers.do</t>
+  </si>
+  <si>
+    <t>4030</t>
+  </si>
+  <si>
+    <t>Figure B15 - college_entrants_multiple_cutoffs_count.png</t>
+  </si>
+  <si>
+    <t>code/stata/27.Tables_Figures_model_numbers.do</t>
+  </si>
+  <si>
+    <t>4241</t>
+  </si>
+  <si>
+    <t>Table C1 - summary_stats_geog_regular_PACE.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>554</t>
+  </si>
+  <si>
+    <t>Table C2 - List_Majors.tex</t>
+  </si>
+  <si>
+    <t>code/tex/List_Majors.tex</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Table C3 - summary_statistics_target_population.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>593</t>
+  </si>
+  <si>
+    <t>Table C4 - TE_applications_admissions.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>687</t>
+  </si>
+  <si>
+    <t>Table C5 - TE_enrolled_over_time.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>788</t>
+  </si>
+  <si>
+    <t>Table C6 - TE_enrolled_over_time_top15.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>864</t>
+  </si>
+  <si>
+    <t>Table C7 - summary_stats_outcomes_TC.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>956</t>
+  </si>
+  <si>
+    <t>Table C8 - TE_effort_items.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>1026</t>
+  </si>
+  <si>
+    <t>Table C9 - TE_psu.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>1122</t>
+  </si>
+  <si>
+    <t>Table C10 - TE_enrolled_over_time_STEM.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>1189</t>
+  </si>
+  <si>
+    <t>Table C11 - TE_enrolled_over_time_top15_STEM.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>1271</t>
+  </si>
+  <si>
+    <t>Table C12 - RCT_selectivity_distance_only_selective.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>1350</t>
+  </si>
+  <si>
+    <t>Table C13 - leebounds_selectivity_distance_only_selective.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>1423</t>
+  </si>
+  <si>
+    <t>Table C14 - TE_college_entrants.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>1466</t>
+  </si>
+  <si>
+    <t>Table C15 - persistence_SUA.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>1532</t>
+  </si>
+  <si>
+    <t>Table C16 - belief_elicitation.tex</t>
+  </si>
+  <si>
+    <t>code/tex/belief_elicitation.tex</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Table C17 - correlates_belief_biases.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>1573</t>
+  </si>
+  <si>
+    <t>Table C18 - p_graduate_reg_whole_sample.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>1621</t>
+  </si>
+  <si>
+    <t>Table C19 - summary_perceived_returns_construction.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>1675</t>
+  </si>
+  <si>
+    <t>Table C20 - params_outside_model_regularadm.tex</t>
+  </si>
+  <si>
+    <t>code/stata/11.Data_for_model_estimation_rescale.do</t>
+  </si>
+  <si>
+    <t>279</t>
+  </si>
+  <si>
+    <t>Table C21 - params_outside_model_rescale.tex</t>
+  </si>
+  <si>
+    <t>code/stata/11.Data_for_model_estimation_rescale.do</t>
+  </si>
+  <si>
+    <t>368</t>
+  </si>
+  <si>
+    <t>Table C22 - structural_model_estimates_edited.tex</t>
+  </si>
+  <si>
+    <t>code/python/add_params_ses_to_table_csv_estimates.py</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>Table C23 - summary_stats_outcomes_model_fit.tex</t>
+  </si>
+  <si>
+    <t>code/stata/27.Tables_Figures_model_numbers.do</t>
+  </si>
+  <si>
+    <t>1665</t>
+  </si>
+  <si>
+    <t>Table C24 - fit_TE_moments_adm_enr_per.tex</t>
+  </si>
+  <si>
+    <t>code/stata/27.Tables_Figures_model_numbers.do</t>
+  </si>
+  <si>
+    <t>1879</t>
+  </si>
+  <si>
+    <t>Table D1 - in_out_flow.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>1835</t>
+  </si>
+  <si>
+    <t>Table D2 - attrition_both.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>1866</t>
+  </si>
+  <si>
+    <t>Table D3 - leebounds_effort_achievement.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>1923</t>
+  </si>
+  <si>
+    <t>Table D4 - validate_achievement_effort.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>1956</t>
+  </si>
+  <si>
+    <t>Table D5 - tab_reduced_form_irt.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>2049</t>
+  </si>
+  <si>
+    <t>Table D6 - TE_subjective_expectations_michela.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>2102</t>
+  </si>
+  <si>
+    <t>Table D7 - sample_balance_within_med_exp_PSU.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>2176</t>
+  </si>
+  <si>
+    <t>Table D8 - validate_beliefs.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>2223</t>
+  </si>
+  <si>
+    <t>Figure D1 - type_histogram_2types.png; type_histogram_3types.png</t>
+  </si>
+  <si>
+    <t>code/stata/27.Tables_Figures_model_numbers.do</t>
+  </si>
+  <si>
+    <t>5130; 5139</t>
+  </si>
+  <si>
+    <t>Table D9 - summary_stats_outcomes_3types.tex</t>
+  </si>
+  <si>
+    <t>code/stata/27.Tables_Figures_model_numbers.do</t>
+  </si>
+  <si>
+    <t>4526</t>
+  </si>
+  <si>
+    <t>Table D10 - TE_pre_college_outcomes_3types.tex</t>
+  </si>
+  <si>
+    <t>code/stata/27.Tables_Figures_model_numbers.do</t>
+  </si>
+  <si>
+    <t>4872</t>
+  </si>
+  <si>
+    <t>Table D11 - fit_TE_moments_adm_enr_per_3types.tex</t>
+  </si>
+  <si>
+    <t>code/stata/27.Tables_Figures_model_numbers.do</t>
+  </si>
+  <si>
+    <t>5063</t>
+  </si>
+  <si>
+    <t>Table E1 - tab_grading.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>2331</t>
+  </si>
+  <si>
+    <t>Table E2 - tab_principal.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>2357</t>
+  </si>
+  <si>
+    <t>Table E3 - teachers_effort.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>2405</t>
+  </si>
+  <si>
+    <t>Table E4 - tab_principal2.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>2433</t>
+  </si>
+  <si>
+    <t>Table E5 - exp_earnings.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>2483</t>
+  </si>
+  <si>
+    <t>Figure F1 - histogram_quality_regular_T_C_comb.png</t>
+  </si>
+  <si>
+    <t>code/stata/10.Figures.do</t>
+  </si>
+  <si>
+    <t>948</t>
+  </si>
+  <si>
+    <t>Figure F2 - histogram_quality_T_PACE_regular_top15_comb.png</t>
+  </si>
+  <si>
+    <t>code/stata/10.Figures.do</t>
+  </si>
+  <si>
+    <t>960</t>
+  </si>
+  <si>
+    <t>Figure F3 - histogram_distance_regular_T_C_comb.png</t>
+  </si>
+  <si>
+    <t>code/stata/10.Figures.do</t>
+  </si>
+  <si>
+    <t>972</t>
+  </si>
+  <si>
+    <t>Figure F4 - histogram_distance_top15_comb.png</t>
+  </si>
+  <si>
+    <t>code/stata/10.Figures.do</t>
+  </si>
+  <si>
+    <t>983</t>
+  </si>
+  <si>
+    <t>Figure F5 - histogram_field_regular_T_C_comb.png</t>
+  </si>
+  <si>
+    <t>code/stata/10.Figures.do</t>
+  </si>
+  <si>
+    <t>994</t>
+  </si>
+  <si>
+    <t>Figure F6 - histogram_field_T_PACE_regular_top15_comb.png</t>
+  </si>
+  <si>
+    <t>code/stata/10.Figures.do</t>
+  </si>
+  <si>
+    <t>1005</t>
+  </si>
+  <si>
+    <t>Table F1 - TE_regular_admissions_enrollments_f.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>2598</t>
+  </si>
+  <si>
+    <t>Table F2 - summary_stats_applications_assignments_top15_all.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>2664</t>
+  </si>
+  <si>
+    <t>Table F3 - TE_applications_assignments_top15.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>2800</t>
+  </si>
+  <si>
+    <t>Table F4 - differences_pace_regular_for_treated_top15.tex</t>
+  </si>
+  <si>
+    <t>code/stata/9.Tables.do</t>
+  </si>
+  <si>
+    <t>2921</t>
+  </si>
+  <si>
+    <t>Figure G1 - PSU_GPA_ppersist_belief_GoF.png</t>
+  </si>
+  <si>
+    <t>code/stata/10.Figures.do</t>
+  </si>
+  <si>
+    <t>1417</t>
+  </si>
+  <si>
+    <t>Table G1 - params_outside_model_PSUbGPAb.tex</t>
+  </si>
+  <si>
+    <t>code/stata/11.Data_for_model_estimation_rescale.do</t>
+  </si>
+  <si>
+    <t>591</t>
+  </si>
+  <si>
+    <t>Figure G2 - PSUbGPAb_belief_GoF_nolasso.png</t>
+  </si>
+  <si>
+    <t>code/stata/11.Data_for_model_estimation_rescale.do</t>
+  </si>
+  <si>
+    <t>635</t>
+  </si>
+  <si>
+    <t>Table G2 - Targeted parameters from descriptive regressions</t>
+  </si>
+  <si>
+    <t>code/tex/auxiliary_parameters.tex</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>Table G3 - Targeted parameters from regressions linking endogenous model outcomes</t>
+  </si>
+  <si>
+    <t>code/tex/auxiliary_parameters.tex</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>Figure H1 - college_entrants_info_count.png</t>
+  </si>
+  <si>
+    <t>code/stata/27.Tables_Figures_model_numbers.do</t>
+  </si>
+  <si>
+    <t>3443</t>
+  </si>
+  <si>
     <t>In-text numbers</t>
+  </si>
+  <si>
+    <t>Program</t>
+  </si>
+  <si>
+    <t>Line Number</t>
+  </si>
+  <si>
+    <t>Reproduced?</t>
+  </si>
+  <si>
+    <t>SIMCE gap: targeted schools vs regular entrants</t>
+  </si>
+  <si>
+    <t>code/stata/27b.In_text_numbers.do</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>Year-5 continuous enrollment effect</t>
+  </si>
+  <si>
+    <t>code/stata/27b.In_text_numbers.do</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Year-5 effect as percent of control mean</t>
+  </si>
+  <si>
+    <t>code/stata/27b.In_text_numbers.do</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>p-value for difference between year-5 and year-1 effects</t>
+  </si>
+  <si>
+    <t>code/stata/27b.In_text_numbers.do</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>Top-15 sample year-1 enrollment effect</t>
+  </si>
+  <si>
+    <t>code/stata/27b.In_text_numbers.do</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>Top-15 sample year-5 enrollment effect</t>
+  </si>
+  <si>
+    <t>code/stata/27b.In_text_numbers.do</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>Top-15 p-value: year-5 vs year-1 effects</t>
+  </si>
+  <si>
+    <t>code/stata/27b.In_text_numbers.do</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>Top-15 sample year-1 percent change</t>
+  </si>
+  <si>
+    <t>code/stata/27b.In_text_numbers.do</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>Top-15 sample year-5 percent change</t>
+  </si>
+  <si>
+    <t>code/stata/27b.In_text_numbers.do</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>Estimated shares of model types 1 and 2</t>
+  </si>
+  <si>
+    <t>code/stata/27b.In_text_numbers.do</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>Three-type model share assigned to type 3</t>
+  </si>
+  <si>
+    <t>code/stata/27b.In_text_numbers.do</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>Believed persistence probability</t>
+  </si>
+  <si>
+    <t>code/stata/27b.In_text_numbers.do</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>Actual persistence probability</t>
+  </si>
+  <si>
+    <t>code/stata/27b.In_text_numbers.do</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>College-degree earnings premium belief</t>
+  </si>
+  <si>
+    <t>code/stata/27b.In_text_numbers.do</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>Financial-aid awareness share and p-value</t>
+  </si>
+  <si>
+    <t>code/stata/27b.In_text_numbers.do</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>Correlation between raw GPA and PRN</t>
+  </si>
+  <si>
+    <t>code/stata/27b.In_text_numbers.do</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>Surveyed students: N and percent of enrolled students</t>
+  </si>
+  <si>
+    <t>code/stata/27b.In_text_numbers.do</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>Shares of tertiary enrollments by institution type</t>
+  </si>
+  <si>
+    <t>code/stata/27b.In_text_numbers.do</t>
+  </si>
+  <si>
+    <t>158</t>
+  </si>
+  <si>
+    <t>Family income of targeted students relative to Chile and regular entrants</t>
+  </si>
+  <si>
+    <t>code/stata/27b.In_text_numbers.do</t>
+  </si>
+  <si>
+    <t>172</t>
+  </si>
+  <si>
+    <t>Top-15 targeted-student achievement vs regular entrants</t>
+  </si>
+  <si>
+    <t>code/stata/27b.In_text_numbers.do</t>
+  </si>
+  <si>
+    <t>190</t>
+  </si>
+  <si>
+    <t>Share reporting preparation for PSU</t>
+  </si>
+  <si>
+    <t>code/stata/27b.In_text_numbers.do</t>
+  </si>
+  <si>
+    <t>195</t>
+  </si>
+  <si>
+    <t>Parents not studying beyond secondary education</t>
+  </si>
+  <si>
+    <t>code/stata/27b.In_text_numbers.do</t>
+  </si>
+  <si>
+    <t>202; 207; 209</t>
+  </si>
+  <si>
+    <t>Average minimum PSU required for regular admission</t>
+  </si>
+  <si>
+    <t>code/stata/27b.In_text_numbers.do</t>
+  </si>
+  <si>
+    <t>214</t>
+  </si>
+  <si>
+    <t>Median subjective expectation for PSU score</t>
+  </si>
+  <si>
+    <t>code/stata/27b.In_text_numbers.do</t>
+  </si>
+  <si>
+    <t>217</t>
+  </si>
+  <si>
+    <t>Type-2 share difference among treated college entrants</t>
+  </si>
+  <si>
+    <t>code/stata/27b.In_text_numbers.do</t>
+  </si>
+  <si>
+    <t>233</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>Values differ: Treatment col.2 0.264 vs 0.247, col.4 0.134 vs 0.152, col.6 0.022 vs 0.021; obs. 315 vs 316.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -67,6 +1258,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -89,7 +1286,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -97,9 +1294,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -434,78 +1630,1912 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:E144"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.5" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="5" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="80.5" customWidth="1"/>
+    <col min="2" max="2" width="48.1640625" customWidth="1"/>
+    <col min="3" max="3" width="13.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>2</v>
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>2</v>
+      <c r="A18" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D26" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D27" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D30" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D31" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D32" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D33" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D34" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D35" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D36" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D37" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D38" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D39" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D40" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D41" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D42" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A43" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D43" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D44" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D45" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D46" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A47" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D47" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A48" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D48" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D49" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D50" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D51" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D52" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D53" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D54" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D55" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D56" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A57" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D57" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A58" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D58" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A59" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D59" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A60" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D60" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A61" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D61" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A62" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D62" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A63" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D63" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A64" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D64" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A65" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D65" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D66" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A67" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D67" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D68" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D69" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A70" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D70" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A71" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D71" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A72" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D72" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A73" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D73" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A74" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D74" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A75" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D75" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A76" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D76" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A77" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D77" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A78" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D78" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A79" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D79" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A80" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D80" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A81" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D81" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A82" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D82" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A83" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D83" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A84" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D84" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A85" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D85" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A86" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D86" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A87" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D87" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A88" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D88" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A89" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D89" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A90" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D90" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A91" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D91" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A92" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D92" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A93" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D93" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A94" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D94" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A95" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D95" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A96" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D96" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A97" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D97" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="16" x14ac:dyDescent="0.25">
+      <c r="A98" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D98" t="s">
+        <v>402</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A99" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D99" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A100" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D100" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A101" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D101" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A102" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="D102" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A103" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D103" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A104" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D104" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A105" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D105" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A106" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D106" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A107" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="D107" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A108" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D108" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A109" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D109" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A110" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D110" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A111" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D111" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A112" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D112" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A113" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D113" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A114" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D114" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A115" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="D115" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A116" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="D116" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A119" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A120" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D120" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A121" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D121" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A122" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="D122" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A123" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D123" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A124" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="D124" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A125" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="D125" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A126" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D126" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A127" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D127" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A128" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="D128" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A129" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="D129" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A130" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D130" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A131" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D131" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A132" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="D132" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A133" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="D133" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A134" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="D134" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A135" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="D135" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A136" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="D136" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A137" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="D137" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A138" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="D138" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A139" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D139" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A140" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="D140" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A141" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="D141" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A142" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="D142" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A143" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D143" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A144" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="D144" t="s">
+        <v>401</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/package-output-map.xlsx
+++ b/package-output-map.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/econ0763/Downloads/JPE/JPE-Tincani-20230441/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FA5860D-B1C4-C04E-9D24-35FBA01D3E88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{828DA77C-E48C-B043-AF11-16F87895348D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17360" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="402">
   <si>
     <t>Data Preparation Program</t>
   </si>
@@ -1231,12 +1231,6 @@
   </si>
   <si>
     <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>Values differ: Treatment col.2 0.264 vs 0.247, col.4 0.134 vs 0.152, col.6 0.022 vs 0.021; obs. 315 vs 316.</t>
   </si>
 </sst>
 </file>
@@ -2913,11 +2907,9 @@
         <v>267</v>
       </c>
       <c r="D98" t="s">
-        <v>402</v>
-      </c>
-      <c r="E98" s="4" t="s">
-        <v>403</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="E98" s="4"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
